--- a/data/trans_camb/P44D-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P44D-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,14</t>
+          <t>-8,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-4,23</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,58</t>
+          <t>-4,25; 6,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,28</t>
+          <t>-7,03; 4,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 0,33</t>
+          <t>-18,42; 0,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -2,04</t>
+          <t>-18,97; -2,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,75</t>
+          <t>-10,15; 1,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -0,07</t>
+          <t>-11,06; -0,32</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-88,94%</t>
+          <t>-89,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-68,05%</t>
+          <t>-69,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-98,43; -47,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,41</t>
+          <t>-100,0; 151,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 9,55</t>
+          <t>-90,79; -7,87</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-13,27</t>
+          <t>-9,17</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,95</t>
+          <t>-18,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,66</t>
+          <t>-13,05</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 9,8</t>
+          <t>-21,15; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -2,34</t>
+          <t>-25,95; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 5,92</t>
+          <t>-38,4; 3,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,11; -1,7</t>
+          <t>-41,97; -1,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 2,76</t>
+          <t>-23,15; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -5,61</t>
+          <t>-26,17; -2,13</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-75,56%</t>
+          <t>-52,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-73,47%</t>
+          <t>-73,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-75,56%</t>
+          <t>-62,99%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 134,94</t>
+          <t>-75,08; 155,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-95,98; -32,94</t>
+          <t>-79,35; 47,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,81</t>
+          <t>-100,0; 60,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,87; -21,3</t>
+          <t>-88,09; -21,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,27; 25,78</t>
+          <t>-74,13; 42,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,04; -52,6</t>
+          <t>-79,22; -20,91</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-12,16</t>
+          <t>-11,7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-24,58</t>
+          <t>-25,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,71</t>
+          <t>-17,78</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 37,48</t>
+          <t>-30,99; 36,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 14,51</t>
+          <t>-43,78; 12,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 33,79</t>
+          <t>-45,06; 35,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 3,02</t>
+          <t>-54,46; 3,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 25,68</t>
+          <t>-24,34; 24,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 2,63</t>
+          <t>-39,4; 1,79</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-37,05%</t>
+          <t>-35,63%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-53,53%</t>
+          <t>-55,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,82%</t>
+          <t>-46,01%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,9; 325,98</t>
+          <t>-58,05; 327,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 187,64</t>
+          <t>-72,97; 113,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 150,88</t>
+          <t>-69,97; 184,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 16,07</t>
+          <t>-75,22; 18,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 105,0</t>
+          <t>-47,48; 116,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 15,73</t>
+          <t>-67,32; 12,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-6,32</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-10,74</t>
+          <t>-10,84</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,56</t>
+          <t>-6,89</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 10,62</t>
+          <t>-8,81; 9,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 0,6</t>
+          <t>-12,67; 3,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 1,98</t>
+          <t>-19,17; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -3,42</t>
+          <t>-20,02; -3,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 3,51</t>
+          <t>-10,17; 4,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -3,27</t>
+          <t>-13,46; -1,5</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-48,6%</t>
+          <t>-24,18%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-59,35%</t>
+          <t>-59,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-55,21%</t>
+          <t>-44,43%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 150,78</t>
+          <t>-47,89; 122,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 3,87</t>
+          <t>-60,45; 53,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 23,86</t>
+          <t>-76,46; 39,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,61; -27,11</t>
+          <t>-74,7; -29,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 29,74</t>
+          <t>-50,41; 36,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,29; -31,96</t>
+          <t>-62,03; -12,71</t>
         </is>
       </c>
     </row>
